--- a/data/file_generation/reference/data_119/重复信息_res.xlsx
+++ b/data/file_generation/reference/data_119/重复信息_res.xlsx
@@ -1,37 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0205/ai办公标注/output/data_119/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E632E788-ED38-5647-B8BB-A77F9B83D971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="35840" yWindow="1300" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="姓名重复" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="姓名重复" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+  <si>
+    <t>年级</t>
+  </si>
+  <si>
+    <t>班级</t>
+  </si>
+  <si>
+    <t>姓名</t>
+  </si>
+  <si>
+    <t>身份证号</t>
+  </si>
+  <si>
+    <t>七年级</t>
+  </si>
+  <si>
+    <t>凤C某</t>
+  </si>
+  <si>
+    <t>UEV1C7UM4VDCYI5X</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>八年级</t>
+  </si>
+  <si>
+    <t>LIWSVNQ5VDS1MR0I</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +111,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,78 +435,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
+  <cols>
+    <col min="4" max="4" width="13.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>年级</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>班级</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>身份证号</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>七年级</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
         <v>6</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>凤C某</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2.793378097401468e+17</v>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>八年级</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
         <v>3</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>凤C某</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>8.879197320290204e+17</v>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -639,15 +647,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -655,13 +654,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B4B8A1-AFAC-4EF9-A326-9B84FCB49C49}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2324F28F-4CC7-41D7-A00B-54D53E797A6F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A12E73F-3644-4922-8E01-12C8B67B3EC3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46B6AFFE-694B-456C-A79C-CB5D9F096B71}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B414CDB1-A5CB-4D48-A993-0FB75B31B6E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E8CFA7E-631C-4D7B-BCA0-81E2391E5046}"/>
 </file>